--- a/public/converted/nomenklatura-ot-bah-30-10-26.xlsx
+++ b/public/converted/nomenklatura-ot-bah-30-10-26.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R332"/>
+  <dimension ref="A1:R331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -573,6 +576,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M2" s="2" t="n">
+        <v>1.13</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -620,6 +626,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M3" s="2" t="n">
+        <v>1.5</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -667,6 +676,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M4" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -714,6 +726,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M5" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -761,6 +776,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M6" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -808,6 +826,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M7" s="2" t="n">
+        <v>1.328</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -855,6 +876,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M8" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -902,6 +926,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M9" s="2" t="n">
+        <v>1.16</v>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -949,6 +976,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M10" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -996,6 +1026,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M11" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1043,6 +1076,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M12" s="2" t="n">
+        <v>1.528</v>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1090,6 +1126,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M13" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1137,6 +1176,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M14" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1184,6 +1226,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M15" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1231,6 +1276,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M16" s="2" t="n">
+        <v>1.54</v>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1278,6 +1326,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M17" s="2" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1325,6 +1376,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M18" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1372,6 +1426,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M19" s="2" t="n">
+        <v>1.35</v>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1419,6 +1476,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M20" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1466,6 +1526,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M21" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1513,6 +1576,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M22" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1560,6 +1626,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M23" s="2" t="n">
+        <v>4.451</v>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1607,6 +1676,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M24" s="2" t="n">
+        <v>4.451</v>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1654,6 +1726,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M25" s="2" t="n">
+        <v>4.451</v>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1701,6 +1776,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M26" s="2" t="n">
+        <v>4.451</v>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1748,6 +1826,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M27" s="2" t="n">
+        <v>0.83</v>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1795,6 +1876,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M28" s="2" t="n">
+        <v>0.83</v>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1842,6 +1926,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M29" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1889,6 +1976,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M30" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1936,6 +2026,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M31" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -1983,6 +2076,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M32" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2030,6 +2126,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M33" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2077,6 +2176,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M34" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2124,6 +2226,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M35" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2171,6 +2276,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M36" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2218,6 +2326,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M37" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2265,6 +2376,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M38" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2312,6 +2426,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M39" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2359,6 +2476,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M40" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2406,6 +2526,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M41" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2453,6 +2576,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M42" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2500,6 +2626,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M43" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2547,6 +2676,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M44" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2594,6 +2726,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M45" s="2" t="n">
+        <v>1.12</v>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2641,6 +2776,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M46" s="2" t="n"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2688,6 +2824,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M47" s="2" t="n"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2735,6 +2872,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M48" s="2" t="n"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2782,6 +2920,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M49" s="2" t="n">
+        <v>33.7</v>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2829,6 +2970,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M50" s="2" t="n">
+        <v>1.114</v>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2876,6 +3020,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M51" s="2" t="n">
+        <v>1.25</v>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2923,6 +3070,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M52" s="2" t="n">
+        <v>1.25</v>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2970,6 +3120,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M53" s="2" t="n">
+        <v>2.95</v>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3017,6 +3170,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M54" s="2" t="n">
+        <v>2.95</v>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3064,6 +3220,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M55" s="2" t="n"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3111,6 +3268,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M56" s="2" t="n"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3158,6 +3316,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M57" s="2" t="n">
+        <v>3.46</v>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3205,6 +3366,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M58" s="2" t="n">
+        <v>3.46</v>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3252,6 +3416,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M59" s="2" t="n">
+        <v>3.46</v>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3299,6 +3466,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M60" s="2" t="n">
+        <v>3.46</v>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3346,6 +3516,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M61" s="2" t="n"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3393,6 +3564,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M62" s="2" t="n"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3440,6 +3612,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M63" s="2" t="n">
+        <v>2.72</v>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3487,6 +3662,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M64" s="2" t="n">
+        <v>2.72</v>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3534,6 +3712,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M65" s="2" t="n">
+        <v>2.72</v>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3581,6 +3762,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M66" s="2" t="n">
+        <v>2.72</v>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3628,6 +3812,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M67" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3675,6 +3862,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M68" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3722,6 +3912,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M69" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3769,6 +3962,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M70" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3816,6 +4012,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M71" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3863,6 +4062,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M72" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3910,6 +4112,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M73" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3957,6 +4162,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M74" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4004,6 +4212,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M75" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4051,6 +4262,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M76" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4098,6 +4312,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M77" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4145,6 +4362,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M78" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4192,6 +4412,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M79" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4239,6 +4462,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M80" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4286,6 +4512,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M81" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4333,6 +4562,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M82" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4380,6 +4612,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M83" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4427,6 +4662,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M84" s="2" t="n"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4474,6 +4710,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M85" s="2" t="n">
+        <v>1.58</v>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4521,6 +4760,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M86" s="2" t="n">
+        <v>6.87</v>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4568,6 +4810,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M87" s="2" t="n">
+        <v>6.87</v>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4615,6 +4860,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M88" s="2" t="n">
+        <v>6.87</v>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4662,6 +4910,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M89" s="2" t="n">
+        <v>2.583</v>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4709,6 +4960,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M90" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4756,6 +5010,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M91" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4803,6 +5060,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M92" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4850,6 +5110,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M93" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4897,6 +5160,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M94" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4944,6 +5210,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M95" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4991,6 +5260,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M96" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5038,6 +5310,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M97" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5085,6 +5360,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M98" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O98" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5132,6 +5410,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M99" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5179,6 +5460,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M100" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5226,6 +5510,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M101" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5273,6 +5560,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M102" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5320,6 +5610,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M103" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5367,6 +5660,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M104" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5414,6 +5710,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M105" s="2" t="n"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5461,6 +5758,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M106" s="2" t="n"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5508,6 +5806,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M107" s="2" t="n"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5555,6 +5854,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M108" s="2" t="n"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5602,6 +5902,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M109" s="2" t="n"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5649,6 +5950,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M110" s="2" t="n"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5696,6 +5998,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M111" s="2" t="n"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5743,6 +6046,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M112" s="2" t="n"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5790,6 +6094,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M113" s="2" t="n"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5837,6 +6142,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M114" s="2" t="n"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5884,6 +6190,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M115" s="2" t="n"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5931,6 +6238,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M116" s="2" t="n"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5978,6 +6286,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M117" s="2" t="n"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6025,6 +6334,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M118" s="2" t="n"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6072,6 +6382,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M119" s="2" t="n"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6119,6 +6430,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M120" s="2" t="n"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6166,6 +6478,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M121" s="2" t="n"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6213,6 +6526,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M122" s="2" t="n"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6260,6 +6574,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M123" s="2" t="n"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6307,6 +6622,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M124" s="2" t="n"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6354,6 +6670,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M125" s="2" t="n"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6401,6 +6718,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M126" s="2" t="n"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6448,6 +6766,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M127" s="2" t="n"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6495,6 +6814,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M128" s="2" t="n">
+        <v>6.87</v>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6542,6 +6864,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M129" s="2" t="n">
+        <v>6.87</v>
+      </c>
       <c r="O129" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6589,6 +6914,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M130" s="2" t="n"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6636,6 +6962,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M131" s="2" t="n"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6683,6 +7010,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M132" s="2" t="n"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6730,6 +7058,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M133" s="2" t="n"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6777,6 +7106,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M134" s="2" t="n"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6824,6 +7154,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M135" s="2" t="n"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6871,6 +7202,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M136" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O136" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6918,6 +7252,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M137" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O137" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6965,6 +7302,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M138" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O138" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7012,6 +7352,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M139" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O139" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7059,6 +7402,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M140" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7106,6 +7452,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M141" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7153,6 +7502,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M142" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7200,6 +7552,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M143" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O143" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7247,6 +7602,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M144" s="2" t="n">
+        <v>2.61</v>
+      </c>
       <c r="O144" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7294,6 +7652,9 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M145" s="2" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7303,12 +7664,12 @@
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Гриль REDMOND SteakMaster RGM-M822, Черный/сталь</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Гриль REDMOND SteakMaster RGM-M822, Черный/сталь</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -7340,6 +7701,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -7350,12 +7714,12 @@
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M822, Черный/сталь</t>
+          <t>Гриль REDMOND SteakMaster RGM-M819D, Серебро</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M822, Черный/сталь</t>
+          <t>Гриль REDMOND SteakMaster RGM-M819D, Серебро</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -7387,6 +7751,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -7397,12 +7764,12 @@
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M819D, Серебро</t>
+          <t>Гриль REDMOND SteakMaster RGM-M817D, Черный/сталь</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M819D, Серебро</t>
+          <t>Гриль REDMOND SteakMaster RGM-M817D, Черный/сталь</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -7434,6 +7801,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -7444,12 +7814,12 @@
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M817D, Черный/сталь</t>
+          <t>Гриль REDMOND SteakMaster RGM-M805, Черный/сталь</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M817D, Черный/сталь</t>
+          <t>Гриль REDMOND SteakMaster RGM-M805, Черный/сталь</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -7481,6 +7851,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -7491,12 +7864,12 @@
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M805, Черный/сталь</t>
+          <t>Гриль REDMOND SteakMaster RGM-M800, Черный/сталь</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M805, Черный/сталь</t>
+          <t>Гриль REDMOND SteakMaster RGM-M800, Черный/сталь</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -7528,6 +7901,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -7538,12 +7914,12 @@
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M800, Черный/сталь</t>
+          <t>Выпрямитель для волос REDMOND HS1716, Серый</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Гриль REDMOND SteakMaster RGM-M800, Черный/сталь</t>
+          <t>Выпрямитель для волос REDMOND HS1716, Серый</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -7576,6 +7952,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M151" s="2" t="n"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7585,12 +7962,12 @@
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос REDMOND HS1716, Серый</t>
+          <t>Выпрямитель для волос REDMOND HS1714, Красный</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос REDMOND HS1716, Серый</t>
+          <t>Выпрямитель для волос REDMOND HS1714, Красный</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -7623,6 +8000,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M152" s="2" t="n"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7632,12 +8010,12 @@
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос REDMOND HS1714, Красный</t>
+          <t>Выпрямитель для волос Redmond RCI-2329</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос REDMOND HS1714, Красный</t>
+          <t>Выпрямитель для волос Redmond RCI-2329</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -7670,6 +8048,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M153" s="2" t="n"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7679,12 +8058,12 @@
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос Redmond RCI-2329</t>
+          <t>Блендер REDMOND RSB-M3416, Черный/сталь</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос Redmond RCI-2329</t>
+          <t>Блендер REDMOND RSB-M3416, Черный/сталь</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7716,6 +8095,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M154" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -7726,12 +8108,12 @@
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RSB-M3416, Черный/сталь</t>
+          <t>Блендер REDMOND RSB-M3407</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RSB-M3416, Черный/сталь</t>
+          <t>Блендер REDMOND RSB-M3407</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -7763,6 +8145,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M155" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -7773,12 +8158,12 @@
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RSB-M3407</t>
+          <t>Блендер REDMOND RSB-M3404, Черный/сталь</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RSB-M3407</t>
+          <t>Блендер REDMOND RSB-M3404, Черный/сталь</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -7810,6 +8195,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -7820,12 +8208,12 @@
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RSB-M3404, Черный/сталь</t>
+          <t>Блендер REDMOND RHB-CB2988, Хром / бронза</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RSB-M3404, Черный/сталь</t>
+          <t>Блендер REDMOND RHB-CB2988, Хром / бронза</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -7857,6 +8245,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M157" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -7867,12 +8258,12 @@
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-CB2988, Хром / бронза</t>
+          <t>Блендер REDMOND RHB-2980, Черный/сталь</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-CB2988, Хром / бронза</t>
+          <t>Блендер REDMOND RHB-2980, Черный/сталь</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -7904,6 +8295,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M158" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -7914,12 +8308,12 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-2980, Черный/сталь</t>
+          <t>Блендер REDMOND RHB-2964, Черный / хром</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-2980, Черный/сталь</t>
+          <t>Блендер REDMOND RHB-2964, Черный / хром</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7951,6 +8345,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M159" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -7961,12 +8358,12 @@
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-2964, Черный / хром</t>
+          <t>Блендер REDMOND RHB-2954, Черный</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-2964, Черный / хром</t>
+          <t>Блендер REDMOND RHB-2954, Черный</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -7998,6 +8395,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M160" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -8008,12 +8408,12 @@
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-2954, Черный</t>
+          <t>Блендер REDMOND BS415</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Блендер REDMOND RHB-2954, Черный</t>
+          <t>Блендер REDMOND BS415</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -8045,6 +8445,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M161" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -8055,12 +8458,12 @@
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BS415</t>
+          <t>Блендер REDMOND BS410</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BS415</t>
+          <t>Блендер REDMOND BS410</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -8092,6 +8495,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M162" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -8102,12 +8508,12 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BS410</t>
+          <t>Блендер REDMOND BH409</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BS410</t>
+          <t>Блендер REDMOND BH409</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -8139,6 +8545,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M163" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -8149,12 +8558,12 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH409</t>
+          <t>Блендер REDMOND BH408</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH409</t>
+          <t>Блендер REDMOND BH408</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -8186,6 +8595,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -8196,12 +8608,12 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH408</t>
+          <t>Блендер REDMOND BH407</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH408</t>
+          <t>Блендер REDMOND BH407</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -8233,6 +8645,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M165" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -8243,12 +8658,12 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH407</t>
+          <t>Блендер REDMOND BH406</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH407</t>
+          <t>Блендер REDMOND BH406</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -8280,6 +8695,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M166" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -8290,12 +8708,12 @@
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH406</t>
+          <t>Блендер REDMOND BH405</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH406</t>
+          <t>Блендер REDMOND BH405</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -8327,6 +8745,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M167" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -8337,12 +8758,12 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH405</t>
+          <t>Блендер REDMOND BH404</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH405</t>
+          <t>Блендер REDMOND BH404</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -8374,6 +8795,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -8384,12 +8808,12 @@
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH404</t>
+          <t>Блендер REDMOND BH403</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH404</t>
+          <t>Блендер REDMOND BH403</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -8421,6 +8845,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M169" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -8431,12 +8858,12 @@
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH403</t>
+          <t>Блендер REDMOND BH402</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH403</t>
+          <t>Блендер REDMOND BH402</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8468,6 +8895,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -8478,12 +8908,12 @@
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH402</t>
+          <t>Блендер REDMOND BH401</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH402</t>
+          <t>Блендер REDMOND BH401</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -8515,6 +8945,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -8525,12 +8958,12 @@
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH401</t>
+          <t>Блендер REDMOND BH400</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH401</t>
+          <t>Блендер REDMOND BH400</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -8562,6 +8995,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -8572,12 +9008,12 @@
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH400</t>
+          <t>Пылесос-робот RED SOLUTION RV-RL6100S, Черный</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Блендер REDMOND BH400</t>
+          <t>Пылесос-робот RED SOLUTION RV-RL6100S, Черный</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -8609,6 +9045,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -8619,12 +9058,12 @@
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-RL6100S, Черный</t>
+          <t>Пылесос-робот RED SOLUTION RV-RL6000S, Черный</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-RL6100S, Черный</t>
+          <t>Пылесос-робот RED SOLUTION RV-RL6000S, Черный</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -8656,6 +9095,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -8666,12 +9108,12 @@
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-RL6000S, Черный</t>
+          <t>Пылесос-робот RED SOLUTION RV-R6070S, Белый</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-RL6000S, Черный</t>
+          <t>Пылесос-робот RED SOLUTION RV-R6070S, Белый</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -8703,6 +9145,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -8713,12 +9158,12 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-R6070S, Белый</t>
+          <t>Пылесос контейнерный RED SOLUTION C330, синий</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-R6070S, Белый</t>
+          <t>Пылесос контейнерный RED SOLUTION C330, синий</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -8750,6 +9195,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -8760,12 +9208,12 @@
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>Пылесос контейнерный RED SOLUTION C330, синий</t>
+          <t>Пылесос вертикальный RED SOLUTION RV-UR362, Черный</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Пылесос контейнерный RED SOLUTION C330, синий</t>
+          <t>Пылесос вертикальный RED SOLUTION RV-UR362, Черный</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -8797,6 +9245,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -8807,12 +9258,12 @@
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION RV-UR362, Черный</t>
+          <t>Пылесос вертикальный RED EVOLUTION RV-UR383, черный</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION RV-UR362, Черный</t>
+          <t>Пылесос вертикальный RED EVOLUTION RV-UR383, черный</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -8844,6 +9295,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -8854,12 +9308,12 @@
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED EVOLUTION RV-UR383, черный</t>
+          <t>Пылесос вертикальный RED SOLUTION V3090, серый</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED EVOLUTION RV-UR383, черный</t>
+          <t>Пылесос вертикальный RED SOLUTION V3090, серый</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -8891,6 +9345,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -8901,12 +9358,12 @@
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION V3090, серый</t>
+          <t>Пылесос вертикальный RED SOLUTION V3080, серый</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION V3090, серый</t>
+          <t>Пылесос вертикальный RED SOLUTION V3080, серый</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -8938,6 +9395,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -8948,12 +9408,12 @@
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION V3080, серый</t>
+          <t>Парогенератор RED SOLUTION RSS-5907, Фиолетовый</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION V3080, серый</t>
+          <t>Парогенератор RED SOLUTION RSS-5907, Фиолетовый</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -8985,6 +9445,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>2.583</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -8995,12 +9458,12 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>Парогенератор RED SOLUTION RSS-5907, Фиолетовый</t>
+          <t>Блендер RED SOLUTION RSB-M3404, Черный/сталь</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Парогенератор RED SOLUTION RSS-5907, Фиолетовый</t>
+          <t>Блендер RED SOLUTION RSB-M3404, Черный/сталь</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -9032,6 +9495,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -9042,12 +9508,12 @@
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t>Блендер RED SOLUTION RSB-M3404, Черный/сталь</t>
+          <t>Кофеварка RED EVOLUTION RCM-1532, Темно-серый</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Блендер RED SOLUTION RSB-M3404, Черный/сталь</t>
+          <t>Кофеварка RED EVOLUTION RCM-1532, Темно-серый</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -9079,6 +9545,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -9089,12 +9558,12 @@
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t>Кофеварка RED EVOLUTION RCM-1532, Темно-серый</t>
+          <t>Планетарный миксер RED EVOLUTION RFM-538, Тёмно-серый</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Кофеварка RED EVOLUTION RCM-1532, Темно-серый</t>
+          <t>Планетарный миксер RED EVOLUTION RFM-538, Тёмно-серый</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -9126,6 +9595,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>6.87</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -9136,12 +9608,12 @@
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t>Планетарный миксер RED EVOLUTION RFM-538, Тёмно-серый</t>
+          <t>Планетарный миксер RED SOLUTION RFM-5355</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Планетарный миксер RED EVOLUTION RFM-538, Тёмно-серый</t>
+          <t>Планетарный миксер RED SOLUTION RFM-5355</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -9173,6 +9645,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>6.87</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -9183,12 +9658,12 @@
     <row r="186">
       <c r="B186" t="inlineStr">
         <is>
-          <t>Планетарный миксер RED SOLUTION RFM-5355</t>
+          <t>Увлажнитель воздуха RED EVOLUTION RHF-3305, Тёмно-серый</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Планетарный миксер RED SOLUTION RFM-5355</t>
+          <t>Увлажнитель воздуха RED EVOLUTION RHF-3305, Тёмно-серый</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -9220,6 +9695,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>1.114</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -9230,12 +9708,12 @@
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t>Увлажнитель воздуха RED EVOLUTION RHF-3305, Тёмно-серый</t>
+          <t>Мясорубка RED EVOLUTION RMG-126, Тёмно-серый</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Увлажнитель воздуха RED EVOLUTION RHF-3305, Тёмно-серый</t>
+          <t>Мясорубка RED EVOLUTION RMG-126, Тёмно-серый</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -9267,6 +9745,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>3.4</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -9277,12 +9758,12 @@
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t>Мясорубка RED EVOLUTION RMG-126, Тёмно-серый</t>
+          <t>Мультиварка RED SOLUTION SkyCooker RMC-M224S, Черный</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Мясорубка RED EVOLUTION RMG-126, Тёмно-серый</t>
+          <t>Мультиварка RED SOLUTION SkyCooker RMC-M224S, Черный</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -9315,6 +9796,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M188" s="2" t="n"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -9324,12 +9806,12 @@
     <row r="189">
       <c r="B189" t="inlineStr">
         <is>
-          <t>Мультиварка RED SOLUTION SkyCooker RMC-M224S, Черный</t>
+          <t>Вакуумный упаковщик RED SOLUTION VSM030, Чёрный</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Мультиварка RED SOLUTION SkyCooker RMC-M224S, Черный</t>
+          <t>Вакуумный упаковщик RED SOLUTION VSM030, Чёрный</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -9362,6 +9844,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M189" s="2" t="n"/>
       <c r="O189" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -9371,12 +9854,12 @@
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
-          <t>Вакуумный упаковщик RED SOLUTION VSM030, Чёрный</t>
+          <t>Весы кухонные RED EVOLUTION RS-M706, Темно-серый</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Вакуумный упаковщик RED SOLUTION VSM030, Чёрный</t>
+          <t>Весы кухонные RED EVOLUTION RS-M706, Темно-серый</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -9408,6 +9891,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>1.01</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -9418,12 +9904,12 @@
     <row r="191">
       <c r="B191" t="inlineStr">
         <is>
-          <t>Весы кухонные RED EVOLUTION RS-M706, Темно-серый</t>
+          <t>Чайник RED SOLUTION COLORSENSE KG1330D, Чёрный</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Весы кухонные RED EVOLUTION RS-M706, Темно-серый</t>
+          <t>Чайник RED SOLUTION COLORSENSE KG1330D, Чёрный</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -9455,6 +9941,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>1.772</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -9465,12 +9954,12 @@
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION COLORSENSE KG1330D, Чёрный</t>
+          <t>Чайник RED SOLUTION RK-M157, Серый</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION COLORSENSE KG1330D, Чёрный</t>
+          <t>Чайник RED SOLUTION RK-M157, Серый</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -9502,6 +9991,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>1.1</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -9512,12 +10004,12 @@
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M157, Серый</t>
+          <t>Чайник RED SOLUTION SkyKettle RK-G200S</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M157, Серый</t>
+          <t>Чайник RED SOLUTION SkyKettle RK-G200S</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -9549,6 +10041,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>1.4</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -9559,12 +10054,12 @@
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION SkyKettle RK-G200S</t>
+          <t>Чайник RED SOLUTION RK-M1721, Сталь</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION SkyKettle RK-G200S</t>
+          <t>Чайник RED SOLUTION RK-M1721, Сталь</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -9596,6 +10091,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>1.13</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -9606,12 +10104,12 @@
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M1721, Сталь</t>
+          <t>Чайник RED SOLUTION RK-G194, Черный</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M1721, Сталь</t>
+          <t>Чайник RED SOLUTION RK-G194, Черный</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -9643,6 +10141,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -9653,12 +10154,12 @@
     <row r="196">
       <c r="B196" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-G194, Черный</t>
+          <t>Чайник RED EVOLUTION RK-M110, Тёмно-серый</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-G194, Черный</t>
+          <t>Чайник RED EVOLUTION RK-M110, Тёмно-серый</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -9690,6 +10191,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>1.05</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -9700,12 +10204,12 @@
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
-          <t>Чайник RED EVOLUTION RK-M110, Тёмно-серый</t>
+          <t>Чайник RED SOLUTION RK-M111D, Чёрный</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Чайник RED EVOLUTION RK-M110, Тёмно-серый</t>
+          <t>Чайник RED SOLUTION RK-M111D, Чёрный</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -9737,6 +10241,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -9747,12 +10254,12 @@
     <row r="198">
       <c r="B198" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M111D, Чёрный</t>
+          <t>Чайник RED SOLUTION COLORSENSE AM108D, Чёрный</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M111D, Чёрный</t>
+          <t>Чайник RED SOLUTION COLORSENSE AM108D, Чёрный</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -9784,6 +10291,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>1.1</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -9794,12 +10304,12 @@
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION COLORSENSE AM108D, Чёрный</t>
+          <t>Чайник RED SOLUTION AM101, Чёрный</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION COLORSENSE AM108D, Чёрный</t>
+          <t>Чайник RED SOLUTION AM101, Чёрный</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -9831,6 +10341,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>1.44</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -9841,12 +10354,12 @@
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION AM101, Чёрный</t>
+          <t>Чайник RED SOLUTION SkyKettle RK-M216S, Белый</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION AM101, Чёрный</t>
+          <t>Чайник RED SOLUTION SkyKettle RK-M216S, Белый</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -9878,6 +10391,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -9888,12 +10404,12 @@
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION SkyKettle RK-M216S, Белый</t>
+          <t>Утюг RED SOLUTION RI-C295, Голубой</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION SkyKettle RK-M216S, Белый</t>
+          <t>Утюг RED SOLUTION RI-C295, Голубой</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -9925,6 +10441,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -9935,12 +10454,12 @@
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t>Утюг RED SOLUTION RI-C295, Голубой</t>
+          <t>Утюг RED SOLUTION C300, Белый</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Утюг RED SOLUTION RI-C295, Голубой</t>
+          <t>Утюг RED SOLUTION C300, Белый</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9972,6 +10491,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -9982,12 +10504,12 @@
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t>Утюг RED SOLUTION C300, Белый</t>
+          <t>Отпариватель ручной RED SOLUTION HS700, Темно-серый</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Утюг RED SOLUTION C300, Белый</t>
+          <t>Отпариватель ручной RED SOLUTION HS700, Темно-серый</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -10019,6 +10541,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>0.95</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -10029,12 +10554,12 @@
     <row r="204">
       <c r="B204" t="inlineStr">
         <is>
-          <t>Отпариватель ручной RED SOLUTION HS700, Темно-серый</t>
+          <t>Тостер RED EVOLUTION RT-44, Темно-серый</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Отпариватель ручной RED SOLUTION HS700, Темно-серый</t>
+          <t>Тостер RED EVOLUTION RT-44, Темно-серый</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -10066,6 +10591,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>1.25</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -10076,12 +10604,12 @@
     <row r="205">
       <c r="B205" t="inlineStr">
         <is>
-          <t>Тостер RED EVOLUTION RT-44, Темно-серый</t>
+          <t>Соковыжималка RED SOLUTION RJ-916</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Тостер RED EVOLUTION RT-44, Темно-серый</t>
+          <t>Соковыжималка RED SOLUTION RJ-916</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -10113,6 +10641,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>3.46</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -10123,12 +10654,12 @@
     <row r="206">
       <c r="B206" t="inlineStr">
         <is>
-          <t>Соковыжималка RED SOLUTION RJ-916</t>
+          <t>Соковыжималка RED SOLUTION RJ-914S, Серебро</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Соковыжималка RED SOLUTION RJ-916</t>
+          <t>Соковыжималка RED SOLUTION RJ-914S, Серебро</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -10160,6 +10691,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>3.46</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -10170,12 +10704,12 @@
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
-          <t>Соковыжималка RED SOLUTION RJ-914S, Серебро</t>
+          <t>Пылесос вертикальный RED SOLUTION RV-UR3200, Серый</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Соковыжималка RED SOLUTION RJ-914S, Серебро</t>
+          <t>Пылесос вертикальный RED SOLUTION RV-UR3200, Серый</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -10207,6 +10741,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -10217,12 +10754,12 @@
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION RV-UR3200, Серый</t>
+          <t>Пылесос контейнерный RED SOLUTION C340, синий</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION RV-UR3200, Серый</t>
+          <t>Пылесос контейнерный RED SOLUTION C340, синий</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -10254,6 +10791,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -10264,12 +10804,12 @@
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t>Пылесос контейнерный RED SOLUTION C340, синий</t>
+          <t>Мультиварка RED EVOLUTION RMC-M51, черный</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Пылесос контейнерный RED SOLUTION C340, синий</t>
+          <t>Мультиварка RED EVOLUTION RMC-M51, черный</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -10302,6 +10842,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M209" s="2" t="n"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10311,12 +10852,12 @@
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t>Мультиварка RED EVOLUTION RMC-M51, черный</t>
+          <t>Мультиварка RED SOLUTION SkyCooker RMC-M40S</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Мультиварка RED EVOLUTION RMC-M51, черный</t>
+          <t>Мультиварка RED SOLUTION SkyCooker RMC-M40S</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -10349,6 +10890,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M210" s="2" t="n"/>
       <c r="O210" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10358,12 +10900,12 @@
     <row r="211">
       <c r="B211" t="inlineStr">
         <is>
-          <t>Мультиварка RED SOLUTION SkyCooker RMC-M40S</t>
+          <t>Мультиварка-скороварка RED SOLUTION COLORSENSE PM4000, Черный</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Мультиварка RED SOLUTION SkyCooker RMC-M40S</t>
+          <t>Мультиварка-скороварка RED SOLUTION COLORSENSE PM4000, Черный</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -10396,6 +10938,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M211" s="2" t="n"/>
       <c r="O211" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10405,12 +10948,12 @@
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка RED SOLUTION COLORSENSE PM4000, Черный</t>
+          <t>Пылесос вертикальный RED SOLUTION V3060, черный</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка RED SOLUTION COLORSENSE PM4000, Черный</t>
+          <t>Пылесос вертикальный RED SOLUTION V3060, черный</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -10442,6 +10985,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -10452,12 +10998,12 @@
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION V3060, черный</t>
+          <t>Кофеварка RED SOLUTION RCM-M1528, Черный</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Пылесос вертикальный RED SOLUTION V3060, черный</t>
+          <t>Кофеварка RED SOLUTION RCM-M1528, Черный</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -10489,6 +11035,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -10499,12 +11048,12 @@
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t>Кофеварка RED SOLUTION RCM-M1528, Черный</t>
+          <t>Гриль RED EVOLUTION SteakPRO RGM-M81, Черный</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Кофеварка RED SOLUTION RCM-M1528, Черный</t>
+          <t>Гриль RED EVOLUTION SteakPRO RGM-M81, Черный</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -10536,6 +11085,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -10546,12 +11098,12 @@
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t>Гриль RED EVOLUTION SteakPRO RGM-M81, Черный</t>
+          <t>Электросушилка RED SOLUTION RFD-0122</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Гриль RED EVOLUTION SteakPRO RGM-M81, Черный</t>
+          <t>Электросушилка RED SOLUTION RFD-0122</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -10583,6 +11135,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>3.9</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -10593,12 +11148,12 @@
     <row r="216">
       <c r="B216" t="inlineStr">
         <is>
-          <t>Электросушилка RED SOLUTION RFD-0122</t>
+          <t>Чайник RED SOLUTION RK-G185, Темно-серый</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Электросушилка RED SOLUTION RFD-0122</t>
+          <t>Чайник RED SOLUTION RK-G185, Темно-серый</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -10630,6 +11185,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -10640,12 +11198,12 @@
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-G185, Темно-серый</t>
+          <t>Чайник RED SOLUTION RK-M158, Черный</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-G185, Темно-серый</t>
+          <t>Чайник RED SOLUTION RK-M158, Черный</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -10677,6 +11235,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>1.528</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -10687,12 +11248,12 @@
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M158, Черный</t>
+          <t>REDMOND VH1311 PRO MAX</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION RK-M158, Черный</t>
+          <t>REDMOND VH1311 PRO MAX</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -10725,6 +11286,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M218" s="2" t="n"/>
       <c r="O218" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10734,12 +11296,12 @@
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t>REDMOND VH1311 PRO MAX</t>
+          <t>Электрический аэрогриль «3 в 1» REDMOND AG1901</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>REDMOND VH1311 PRO MAX</t>
+          <t>Электрический аэрогриль «3 в 1» REDMOND AG1901</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -10771,6 +11333,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>5.66</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -10781,12 +11346,12 @@
     <row r="220">
       <c r="B220" t="inlineStr">
         <is>
-          <t>Электрический аэрогриль «3 в 1» REDMOND AG1901</t>
+          <t>многофункциональная мультиварка REDMOND MC101</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Электрический аэрогриль «3 в 1» REDMOND AG1901</t>
+          <t>многофункциональная мультиварка REDMOND MC101</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -10819,6 +11384,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M220" s="2" t="n"/>
       <c r="O220" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10828,12 +11394,12 @@
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t>многофункциональная мультиварка REDMOND MC101</t>
+          <t>ручной отпариватель для одежды REDMOND SH1634</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>многофункциональная мультиварка REDMOND MC101</t>
+          <t>ручной отпариватель для одежды REDMOND SH1634</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -10865,6 +11431,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>0.95</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -10875,12 +11444,12 @@
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t>ручной отпариватель для одежды REDMOND SH1634</t>
+          <t>льтракомпактный ручной отпариватель REDMOND SH1639</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ручной отпариватель для одежды REDMOND SH1634</t>
+          <t>льтракомпактный ручной отпариватель REDMOND SH1639</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -10912,6 +11481,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>0.95</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -10922,12 +11494,12 @@
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t>льтракомпактный ручной отпариватель REDMOND SH1639</t>
+          <t>выпрямитель для волос REDMOND HS1718</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>льтракомпактный ручной отпариватель REDMOND SH1639</t>
+          <t>выпрямитель для волос REDMOND HS1718</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -10960,6 +11532,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M223" s="2" t="n"/>
       <c r="O223" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10969,12 +11542,12 @@
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t>выпрямитель для волос REDMOND HS1718</t>
+          <t>погружной блендер формата «4 в 1» REDMOND BH420</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>выпрямитель для волос REDMOND HS1718</t>
+          <t>погружной блендер формата «4 в 1» REDMOND BH420</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -11006,6 +11579,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -11016,12 +11592,12 @@
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>погружной блендер формата «4 в 1» REDMOND BH420</t>
+          <t>электрическая мясорубка-мультисистема «7 в 1» REDMOND MG504</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>погружной блендер формата «4 в 1» REDMOND BH420</t>
+          <t>электрическая мясорубка-мультисистема «7 в 1» REDMOND MG504</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -11053,6 +11629,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>3.4</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -11063,12 +11642,12 @@
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t>электрическая мясорубка-мультисистема «7 в 1» REDMOND MG504</t>
+          <t>капсульная кофеварка формата «3 в 1» REDMOND CM713</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>электрическая мясорубка-мультисистема «7 в 1» REDMOND MG504</t>
+          <t>капсульная кофеварка формата «3 в 1» REDMOND CM713</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -11100,6 +11679,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -11110,12 +11692,12 @@
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
-          <t>капсульная кофеварка формата «3 в 1» REDMOND CM713</t>
+          <t>электросушилка для овощей и фруктов — REDMOND FD1105</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>капсульная кофеварка формата «3 в 1» REDMOND CM713</t>
+          <t>электросушилка для овощей и фруктов — REDMOND FD1105</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -11147,6 +11729,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -11157,12 +11742,12 @@
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t>электросушилка для овощей и фруктов — REDMOND FD1105</t>
+          <t>беспроводной электрический чайник REDMOND KG255</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>электросушилка для овощей и фруктов — REDMOND FD1105</t>
+          <t>беспроводной электрический чайник REDMOND KG255</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -11194,6 +11779,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -11204,12 +11792,12 @@
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t>беспроводной электрический чайник REDMOND KG255</t>
+          <t>REDMOND KG254 электрический чайник</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>беспроводной электрический чайник REDMOND KG255</t>
+          <t>REDMOND KG254 электрический чайник</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -11241,6 +11829,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M229" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -11251,12 +11842,12 @@
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t>REDMOND KG254 электрический чайник</t>
+          <t>REDMOND KM244 электрический чайник</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>REDMOND KG254 электрический чайник</t>
+          <t>REDMOND KM244 электрический чайник</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -11288,6 +11879,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M230" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -11298,12 +11892,12 @@
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t>REDMOND KM244 электрический чайник</t>
+          <t>REDMOND KM243 электрический чайник</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>REDMOND KM244 электрический чайник</t>
+          <t>REDMOND KM243 электрический чайник</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -11335,6 +11929,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M231" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -11345,12 +11942,12 @@
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t>REDMOND KM243 электрический чайник</t>
+          <t>REDMOND SkyKettle KM231S электрический чайник</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>REDMOND KM243 электрический чайник</t>
+          <t>REDMOND SkyKettle KM231S электрический чайник</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -11382,6 +11979,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M232" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -11392,12 +11992,12 @@
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t>REDMOND SkyKettle KM231S электрический чайник</t>
+          <t>Аэрогриль RED SOLUTION COLORSENSE W265, серый, черный</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>REDMOND SkyKettle KM231S электрический чайник</t>
+          <t>Аэрогриль RED SOLUTION COLORSENSE W265, серый, черный</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -11429,6 +12029,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M233" s="2" t="n">
+        <v>5.66</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -11439,12 +12042,12 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t>Аэрогриль RED SOLUTION COLORSENSE W265, серый, черный</t>
+          <t>Аэрогриль RED SOLUTION COLORSENSE W260, серый, черный</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Аэрогриль RED SOLUTION COLORSENSE W265, серый, черный</t>
+          <t>Аэрогриль RED SOLUTION COLORSENSE W260, серый, черный</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -11476,6 +12079,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M234" s="2" t="n">
+        <v>5.66</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -11486,12 +12092,12 @@
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t>Аэрогриль RED SOLUTION COLORSENSE W260, серый, черный</t>
+          <t>Утюг RED SOLUTION I281, Белый/чёрный</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Аэрогриль RED SOLUTION COLORSENSE W260, серый, черный</t>
+          <t>Утюг RED SOLUTION I281, Белый/чёрный</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -11523,6 +12129,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M235" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -11533,12 +12142,12 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t>Утюг RED SOLUTION I281, Белый/чёрный</t>
+          <t>компактный робот-пылесос RED evolution RV-R571</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Утюг RED SOLUTION I281, Белый/чёрный</t>
+          <t>компактный робот-пылесос RED evolution RV-R571</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -11570,6 +12179,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M236" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -11580,12 +12192,12 @@
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t>компактный робот-пылесос RED evolution RV-R571</t>
+          <t>Пылесос-робот RED SOLUTION RV-R6060S, Черный</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>компактный робот-пылесос RED evolution RV-R571</t>
+          <t>Пылесос-робот RED SOLUTION RV-R6060S, Черный</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -11617,6 +12229,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M237" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -11627,12 +12242,12 @@
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-R6060S, Черный</t>
+          <t>умный робот-пылесос RED solution RV-R6030S</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Пылесос-робот RED SOLUTION RV-R6060S, Черный</t>
+          <t>умный робот-пылесос RED solution RV-R6030S</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -11664,6 +12279,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -11674,12 +12292,12 @@
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t>умный робот-пылесос RED solution RV-R6030S</t>
+          <t>робот-пылесос RED solution RV-R6050S</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>умный робот-пылесос RED solution RV-R6030S</t>
+          <t>робот-пылесос RED solution RV-R6050S</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -11711,6 +12329,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
@@ -11721,12 +12342,12 @@
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t>робот-пылесос RED solution RV-R6050S</t>
+          <t>робот-пылесос RED solution RV-R6040S</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>робот-пылесос RED solution RV-R6050S</t>
+          <t>робот-пылесос RED solution RV-R6040S</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -11758,6 +12379,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -11768,12 +12392,12 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
-          <t>робот-пылесос RED solution RV-R6040S</t>
+          <t>Чайник RED SOLUTION G121, Чёрный</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>робот-пылесос RED solution RV-R6040S</t>
+          <t>Чайник RED SOLUTION G121, Чёрный</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -11805,6 +12429,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M241" s="2" t="n">
+        <v>1.1</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -11815,12 +12442,12 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION G121, Чёрный</t>
+          <t>Чайник RED COLORSENSE AM120D, Чёрный</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Чайник RED SOLUTION G121, Чёрный</t>
+          <t>Чайник RED COLORSENSE AM120D, Чёрный</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -11852,6 +12479,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M242" s="2" t="n">
+        <v>1.3</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -11862,12 +12492,12 @@
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t>Чайник RED COLORSENSE AM120D, Чёрный</t>
+          <t>многофункциональная мультиварка РЕДМОНД MC104</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Чайник RED COLORSENSE AM120D, Чёрный</t>
+          <t>многофункциональная мультиварка РЕДМОНД MC104</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -11900,6 +12530,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M243" s="2" t="n"/>
       <c r="O243" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -11909,12 +12540,12 @@
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t>многофункциональная мультиварка РЕДМОНД MC104</t>
+          <t>Чайник RED EVOLUTION RK-G20, Тёмно-серый</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>многофункциональная мультиварка РЕДМОНД MC104</t>
+          <t>Чайник RED EVOLUTION RK-G20, Тёмно-серый</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -11946,6 +12577,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>1.334</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -11956,12 +12590,12 @@
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t>Чайник RED EVOLUTION RK-G20, Тёмно-серый</t>
+          <t>электрический чайник REDMOND RK-G196</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Чайник RED EVOLUTION RK-G20, Тёмно-серый</t>
+          <t>электрический чайник REDMOND RK-G196</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -11993,6 +12627,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -12003,12 +12640,12 @@
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t>электрический чайник REDMOND RK-G196</t>
+          <t>Электрический чайник Midea MK-8028</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>электрический чайник REDMOND RK-G196</t>
+          <t>Электрический чайник Midea MK-8028</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -12040,6 +12677,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>1.19</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -12050,12 +12690,12 @@
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-8028</t>
+          <t>Электрический чайник Midea MK-9093</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-8028</t>
+          <t>Электрический чайник Midea MK-9093</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -12087,6 +12727,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>1.39</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -12097,12 +12740,12 @@
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-9093</t>
+          <t>Электрический чайник Midea MK-8076</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-9093</t>
+          <t>Электрический чайник Midea MK-8076</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -12134,6 +12777,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M248" s="2" t="n">
+        <v>1.19</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -12144,12 +12790,12 @@
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-8076</t>
+          <t>Электрический чайник Midea MK-8015</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-8076</t>
+          <t>Электрический чайник Midea MK-8015</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -12181,6 +12827,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>1.19</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -12191,12 +12840,12 @@
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-8015</t>
+          <t>Электрический чайник Hyundai HYK-G3026</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Электрический чайник Midea MK-8015</t>
+          <t>Электрический чайник Hyundai HYK-G3026</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -12228,6 +12877,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>1.09</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -12238,12 +12890,12 @@
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t>Электрический чайник Hyundai HYK-G3026</t>
+          <t>Погружной блендер Midea MC-BL801</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Электрический чайник Hyundai HYK-G3026</t>
+          <t>Погружной блендер Midea MC-BL801</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -12275,6 +12927,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -12285,12 +12940,12 @@
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t>Погружной блендер Midea MC-BL801</t>
+          <t>Мультиварка Comfee CF-MC9501</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Погружной блендер Midea MC-BL801</t>
+          <t>Мультиварка Comfee CF-MC9501</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -12323,6 +12978,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M252" s="2" t="n"/>
       <c r="O252" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12332,12 +12988,12 @@
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
-          <t>Мультиварка Comfee CF-MC9501</t>
+          <t>Электрический утюг Zelmer ZIR2620</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Мультиварка Comfee CF-MC9501</t>
+          <t>Электрический утюг Zelmer ZIR2620</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -12369,6 +13025,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M253" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -12379,12 +13038,12 @@
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
-          <t>Электрический утюг Zelmer ZIR2620</t>
+          <t>Рожковая кофеварка Vitek VT-1511 BK</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Электрический утюг Zelmer ZIR2620</t>
+          <t>Рожковая кофеварка Vitek VT-1511 BK</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -12416,6 +13075,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M254" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -12426,12 +13088,12 @@
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка Vitek VT-1511 BK</t>
+          <t>Настольная индукционная плита Midea MC-IN2200</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка Vitek VT-1511 BK</t>
+          <t>Настольная индукционная плита Midea MC-IN2200</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -12463,6 +13125,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M255" s="2" t="n">
+        <v>1.58</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -12473,12 +13138,12 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t>Настольная индукционная плита Midea MC-IN2200</t>
+          <t>Настольная индукционная плита Midea MC-IN2101</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Настольная индукционная плита Midea MC-IN2200</t>
+          <t>Настольная индукционная плита Midea MC-IN2101</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -12510,6 +13175,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M256" s="2" t="n">
+        <v>1.58</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -12520,12 +13188,12 @@
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
-          <t>Настольная индукционная плита Midea MC-IN2101</t>
+          <t>Настольная индукционная плита Midea MC-IN2212</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Настольная индукционная плита Midea MC-IN2101</t>
+          <t>Настольная индукционная плита Midea MC-IN2212</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -12557,6 +13225,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M257" s="2" t="n">
+        <v>1.58</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -12567,12 +13238,12 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
-          <t>Настольная индукционная плита Midea MC-IN2212</t>
+          <t>Встраиваемая индукционная варочная панель Midea MIH64100</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Настольная индукционная плита Midea MC-IN2212</t>
+          <t>Встраиваемая индукционная варочная панель Midea MIH64100</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -12605,6 +13276,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M258" s="2" t="n"/>
       <c r="O258" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12614,12 +13286,12 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>Встраиваемая индукционная варочная панель Midea MIH64100</t>
+          <t>Встраиваемая индукционная варочная панель Midea MIH67781F</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Встраиваемая индукционная варочная панель Midea MIH64100</t>
+          <t>Встраиваемая индукционная варочная панель Midea MIH67781F</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -12652,6 +13324,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M259" s="2" t="n"/>
       <c r="O259" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12661,12 +13334,12 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t>Встраиваемая индукционная варочная панель Midea MIH67781F</t>
+          <t>Встраиваемая индукционная варочная панель Midea MIH65781SB</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Встраиваемая индукционная варочная панель Midea MIH67781F</t>
+          <t>Встраиваемая индукционная варочная панель Midea MIH65781SB</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -12699,6 +13372,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M260" s="2" t="n"/>
       <c r="O260" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12708,12 +13382,12 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t>Встраиваемая индукционная варочная панель Midea MIH65781SB</t>
+          <t>Миксер RED SOLUTION RHM-M2108, Серебро</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Встраиваемая индукционная варочная панель Midea MIH65781SB</t>
+          <t>Миксер RED SOLUTION RHM-M2108, Серебро</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -12745,6 +13419,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M261" s="2" t="n">
+        <v>6.87</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -12755,12 +13432,12 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t>Миксер RED SOLUTION RHM-M2108, Серебро</t>
+          <t>Вертикальный напо отпариватель Philips 3000 Series STE3170/80</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Миксер RED SOLUTION RHM-M2108, Серебро</t>
+          <t>Вертикальный напо отпариватель Philips 3000 Series STE3170/80</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -12792,6 +13469,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M262" s="2" t="n">
+        <v>0.95</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -12802,12 +13482,12 @@
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t>Вертикальный напо отпариватель Philips 3000 Series STE3170/80</t>
+          <t>Вертикальный отпариватель Tefal Pro Style Care IT8480E1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Вертикальный напо отпариватель Philips 3000 Series STE3170/80</t>
+          <t>Вертикальный отпариватель Tefal Pro Style Care IT8480E1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -12839,6 +13519,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M263" s="2" t="n">
+        <v>0.95</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -12849,12 +13532,12 @@
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
-          <t>Вертикальный отпариватель Tefal Pro Style Care IT8480E1</t>
+          <t>Робот-пылесос Vitek VT-1802</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Вертикальный отпариватель Tefal Pro Style Care IT8480E1</t>
+          <t>Робот-пылесос Vitek VT-1802</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -12886,6 +13569,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M264" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
@@ -12896,12 +13582,12 @@
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t>Робот-пылесос Vitek VT-1802</t>
+          <t>Мультиварка-скороварка Midea MPC-6039</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Робот-пылесос Vitek VT-1802</t>
+          <t>Мультиварка-скороварка Midea MPC-6039</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -12934,6 +13620,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M265" s="2" t="n"/>
       <c r="O265" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12943,12 +13630,12 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка Midea MPC-6039</t>
+          <t>Выпрямитель для волос Rowenta Karl Lagerfeld Easyliss SF161LF0</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка Midea MPC-6039</t>
+          <t>Выпрямитель для волос Rowenta Karl Lagerfeld Easyliss SF161LF0</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -12981,6 +13668,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M266" s="2" t="n"/>
       <c r="O266" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12990,12 +13678,12 @@
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос Rowenta Karl Lagerfeld Easyliss SF161LF0</t>
+          <t>Электрический утюг Zelmer ZIR3000 STIRO</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Выпрямитель для волос Rowenta Karl Lagerfeld Easyliss SF161LF0</t>
+          <t>Электрический утюг Zelmer ZIR3000 STIRO</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -13027,6 +13715,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M267" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -13037,12 +13728,12 @@
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t>Электрический утюг Zelmer ZIR3000 STIRO</t>
+          <t>Шнековая соковыжималка RED SOLUTION RJ-914S</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Электрический утюг Zelmer ZIR3000 STIRO</t>
+          <t>Шнековая соковыжималка RED SOLUTION RJ-914S</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -13074,6 +13765,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M268" s="2" t="n">
+        <v>3.46</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -13084,12 +13778,12 @@
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t>Шнековая соковыжималка RED SOLUTION RJ-914S</t>
+          <t>Электрический чайник RAF R.7941</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Шнековая соковыжималка RED SOLUTION RJ-914S</t>
+          <t>Электрический чайник RAF R.7941</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -13121,6 +13815,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M269" s="2" t="n">
+        <v>1.09</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -13131,12 +13828,12 @@
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>Электрический чайник RAF R.7941</t>
+          <t>Электрический утюг Hyundai H-SI01221</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Электрический чайник RAF R.7941</t>
+          <t>Электрический утюг Hyundai H-SI01221</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -13168,6 +13865,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M270" s="2" t="n">
+        <v>1.12</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -13178,12 +13878,12 @@
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>Электрический утюг Hyundai H-SI01221</t>
+          <t>Кофемашина RED SOLUTION Colomba RCM-1550, Черно-серый</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Электрический утюг Hyundai H-SI01221</t>
+          <t>Кофемашина RED SOLUTION Colomba RCM-1550, Черно-серый</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -13215,6 +13915,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M271" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -13225,12 +13928,12 @@
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>Кофемашина RED SOLUTION Colomba RCM-1550, Черно-серый</t>
+          <t>Кофемашина RED SOLUTION Indi RCM-1540, Черно-серый</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Кофемашина RED SOLUTION Colomba RCM-1550, Черно-серый</t>
+          <t>Кофемашина RED SOLUTION Indi RCM-1540, Черно-серый</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -13262,6 +13965,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M272" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -13272,12 +13978,12 @@
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>Кофемашина RED SOLUTION Indi RCM-1540, Черно-серый</t>
+          <t>Робот-пылесос RED SOLUTION R6105</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Кофемашина RED SOLUTION Indi RCM-1540, Черно-серый</t>
+          <t>Робот-пылесос RED SOLUTION R6105</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -13309,6 +14015,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M273" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -13319,12 +14028,12 @@
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>Робот-пылесос RED SOLUTION R6105</t>
+          <t>Робот-пылесос RED SOLUTION Fusion R573</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Робот-пылесос RED SOLUTION R6105</t>
+          <t>Робот-пылесос RED SOLUTION Fusion R573</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -13356,6 +14065,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M274" s="2" t="n">
+        <v>2.72</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -13366,12 +14078,12 @@
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>Робот-пылесос RED SOLUTION Fusion R573</t>
+          <t>Гриль RED SOLUTION SteakPRO RGM-M805, Серый/металл</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Робот-пылесос RED SOLUTION Fusion R573</t>
+          <t>Гриль RED SOLUTION SteakPRO RGM-M805, Серый/металл</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -13403,6 +14115,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M275" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -13413,12 +14128,12 @@
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>Гриль RED SOLUTION SteakPRO RGM-M805, Серый/металл</t>
+          <t>Гриль-духовка RED SOLUTION SteakPRO RGM-M816P, Черный/хром</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Гриль RED SOLUTION SteakPRO RGM-M805, Серый/металл</t>
+          <t>Гриль-духовка RED SOLUTION SteakPRO RGM-M816P, Черный/хром</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -13451,6 +14166,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M276" s="2" t="n"/>
       <c r="O276" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13460,12 +14176,12 @@
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>Гриль-духовка RED SOLUTION SteakPRO RGM-M816P, Черный/хром</t>
+          <t>Гриль-духо RED SOLUTION SteakPRO RGM-G850P, Черный/хром</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Гриль-духовка RED SOLUTION SteakPRO RGM-M816P, Черный/хром</t>
+          <t>Гриль-духо RED SOLUTION SteakPRO RGM-G850P, Черный/хром</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -13497,6 +14213,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M277" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -13507,12 +14226,12 @@
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>Гриль-духо RED SOLUTION SteakPRO RGM-G850P, Черный/хром</t>
+          <t>Беспроводной вертикальный пылесос REDMOND RV-UR375</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Гриль-духо RED SOLUTION SteakPRO RGM-G850P, Черный/хром</t>
+          <t>Беспроводной вертикальный пылесос REDMOND RV-UR375</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -13544,6 +14263,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M278" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -13554,12 +14276,12 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>Беспроводной вертикальный пылесос REDMOND RV-UR375</t>
+          <t>Блендер RED SOLUTION RHB-2981, Черный/шампань</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Беспроводной вертикальный пылесос REDMOND RV-UR375</t>
+          <t>Блендер RED SOLUTION RHB-2981, Черный/шампань</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -13591,6 +14313,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M279" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -13601,12 +14326,12 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>Блендер RED SOLUTION RHB-2981, Черный/шампань</t>
+          <t>Блендер RED SOLUTION HB2902, Чёрный</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Блендер RED SOLUTION RHB-2981, Черный/шампань</t>
+          <t>Блендер RED SOLUTION HB2902, Чёрный</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -13638,6 +14363,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M280" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -13648,12 +14376,12 @@
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>Блендер RED SOLUTION HB2902, Чёрный</t>
+          <t>Ультразвуковой увлажнитель RED SOLUTION RHF-3340, Белый</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Блендер RED SOLUTION HB2902, Чёрный</t>
+          <t>Ультразвуковой увлажнитель RED SOLUTION RHF-3340, Белый</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -13685,6 +14413,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M281" s="2" t="n">
+        <v>1.114</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -13695,12 +14426,12 @@
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>Ультразвуковой увлажнитель RED SOLUTION RHF-3340, Белый</t>
+          <t>Вертикальный отпариватель Redmond SV1651</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ультразвуковой увлажнитель RED SOLUTION RHF-3340, Белый</t>
+          <t>Вертикальный отпариватель Redmond SV1651</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -13732,6 +14463,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M282" s="2" t="n">
+        <v>0.95</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -13742,12 +14476,12 @@
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>Вертикальный отпариватель Redmond SV1651</t>
+          <t>Аэрогриль REDMOND AG1900</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Вертикальный отпариватель Redmond SV1651</t>
+          <t>Аэрогриль REDMOND AG1900</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -13779,6 +14513,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M283" s="2" t="n">
+        <v>5.66</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -13789,12 +14526,12 @@
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>Аэрогриль REDMOND AG1900</t>
+          <t>Электрогриль REDMOND SteakMaster GM303</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Аэрогриль REDMOND AG1900</t>
+          <t>Электрогриль REDMOND SteakMaster GM303</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -13826,6 +14563,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M284" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -13836,12 +14576,12 @@
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>Электрогриль REDMOND SteakMaster GM303</t>
+          <t>Мультиварка-скороварка REDMOND Fast Chef MP111</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Электрогриль REDMOND SteakMaster GM303</t>
+          <t>Мультиварка-скороварка REDMOND Fast Chef MP111</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -13874,6 +14614,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M285" s="2" t="n"/>
       <c r="O285" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13883,12 +14624,12 @@
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка REDMOND Fast Chef MP111</t>
+          <t>Рожковая кофеварка REDMOND CM716</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка REDMOND Fast Chef MP111</t>
+          <t>Рожковая кофеварка REDMOND CM716</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -13920,6 +14661,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M286" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -13930,12 +14674,12 @@
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка REDMOND CM716</t>
+          <t>Вакуумный упаковщик Redmond VS1500</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка REDMOND CM716</t>
+          <t>Вакуумный упаковщик Redmond VS1500</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -13968,6 +14712,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M287" s="2" t="n"/>
       <c r="O287" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13977,12 +14722,12 @@
     <row r="288">
       <c r="B288" t="inlineStr">
         <is>
-          <t>Вакуумный упаковщик Redmond VS1500</t>
+          <t>Вакуумный упаковщик REDMOND VS1501</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Вакуумный упаковщик Redmond VS1500</t>
+          <t>Вакуумный упаковщик REDMOND VS1501</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -14015,6 +14760,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M288" s="2" t="n"/>
       <c r="O288" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14024,12 +14770,12 @@
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>Вакуумный упаковщик REDMOND VS1501</t>
+          <t>Электросушилка REDMOND FD1105</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Вакуумный упаковщик REDMOND VS1501</t>
+          <t>Электросушилка REDMOND FD1105</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -14061,6 +14807,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M289" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -14071,12 +14820,12 @@
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>Электросушилка REDMOND FD1105</t>
+          <t>Электросушилка Redmond FD1106</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Электросушилка REDMOND FD1105</t>
+          <t>Электросушилка Redmond FD1106</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -14108,6 +14857,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M290" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -14118,12 +14870,12 @@
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>Электросушилка Redmond FD1106</t>
+          <t>Мультиварка-скороварка REDMOND Fast Chef MP112</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Электросушилка Redmond FD1106</t>
+          <t>Мультиварка-скороварка REDMOND Fast Chef MP112</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -14156,6 +14908,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M291" s="2" t="n"/>
       <c r="O291" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14165,12 +14918,12 @@
     <row r="292">
       <c r="B292" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка REDMOND Fast Chef MP112</t>
+          <t>Мультиварка REDMOND MC101</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Мультиварка-скороварка REDMOND Fast Chef MP112</t>
+          <t>Мультиварка REDMOND MC101</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -14203,6 +14956,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M292" s="2" t="n"/>
       <c r="O292" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14212,12 +14966,12 @@
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>Мультиварка REDMOND MC101</t>
+          <t>Мультиварка Redmond MC123</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Мультиварка REDMOND MC101</t>
+          <t>Мультиварка Redmond MC123</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -14250,6 +15004,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M293" s="2" t="n"/>
       <c r="O293" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14259,12 +15014,12 @@
     <row r="294">
       <c r="B294" t="inlineStr">
         <is>
-          <t>Мультиварка Redmond MC123</t>
+          <t>Рожковая кофеварка REDMOND CM715</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Мультиварка Redmond MC123</t>
+          <t>Рожковая кофеварка REDMOND CM715</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -14296,6 +15051,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M294" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -14306,12 +15064,12 @@
     <row r="295">
       <c r="B295" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка REDMOND CM715</t>
+          <t>Рожковая кофеварка Redmond CM717</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка REDMOND CM715</t>
+          <t>Рожковая кофеварка Redmond CM717</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -14343,6 +15101,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M295" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -14353,12 +15114,12 @@
     <row r="296">
       <c r="B296" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка Redmond CM717</t>
+          <t>Капельная кофеварка REDMOND CM712</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка Redmond CM717</t>
+          <t>Капельная кофеварка REDMOND CM712</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -14390,6 +15151,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M296" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -14400,12 +15164,12 @@
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
-          <t>Капельная кофеварка REDMOND CM712</t>
+          <t>Капсульная кофемашина 3-в-1 REDMOND CM713</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Капельная кофеварка REDMOND CM712</t>
+          <t>Капсульная кофемашина 3-в-1 REDMOND CM713</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -14437,6 +15201,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M297" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -14447,12 +15214,12 @@
     <row r="298">
       <c r="B298" t="inlineStr">
         <is>
-          <t>Капсульная кофемашина 3-в-1 REDMOND CM713</t>
+          <t>Капельная кофеварка REDMOND CM703</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Капсульная кофемашина 3-в-1 REDMOND CM713</t>
+          <t>Капельная кофеварка REDMOND CM703</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -14484,6 +15251,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M298" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -14494,12 +15264,12 @@
     <row r="299">
       <c r="B299" t="inlineStr">
         <is>
-          <t>Капельная кофеварка REDMOND CM703</t>
+          <t>Мультипекарь REDMOND MB1200</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Капельная кофеварка REDMOND CM703</t>
+          <t>Мультипекарь REDMOND MB1200</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -14532,6 +15302,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M299" s="2" t="n"/>
       <c r="O299" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14541,12 +15312,12 @@
     <row r="300">
       <c r="B300" t="inlineStr">
         <is>
-          <t>Мультипекарь REDMOND MB1200</t>
+          <t>Погружной блендер Redmond BH420</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Мультипекарь REDMOND MB1200</t>
+          <t>Погружной блендер Redmond BH420</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -14578,6 +15349,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M300" s="2" t="n">
+        <v>1.61</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -14588,12 +15362,12 @@
     <row r="301">
       <c r="B301" t="inlineStr">
         <is>
-          <t>Погружной блендер Redmond BH420</t>
+          <t>Кухонный комбайн REDMOND FP607</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Погружной блендер Redmond BH420</t>
+          <t>Кухонный комбайн REDMOND FP607</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -14626,6 +15400,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M301" s="2" t="n"/>
       <c r="O301" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14635,12 +15410,12 @@
     <row r="302">
       <c r="B302" t="inlineStr">
         <is>
-          <t>Кухонный комбайн REDMOND FP607</t>
+          <t>Комбайн для детского питания REDMOND Baby BC5202</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Кухонный комбайн REDMOND FP607</t>
+          <t>Комбайн для детского питания REDMOND Baby BC5202</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -14673,6 +15448,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M302" s="2" t="n"/>
       <c r="O302" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14682,12 +15458,12 @@
     <row r="303">
       <c r="B303" t="inlineStr">
         <is>
-          <t>Комбайн для детского питания REDMOND Baby BC5202</t>
+          <t>Вертикальный беспроводной пылесос REDMOND VH1319</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Комбайн для детского питания REDMOND Baby BC5202</t>
+          <t>Вертикальный беспроводной пылесос REDMOND VH1319</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -14719,6 +15495,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M303" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -14729,12 +15508,12 @@
     <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>Вертикальный беспроводной пылесос REDMOND VH1319</t>
+          <t>Кофемашина REDMOND RCM-1517</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Вертикальный беспроводной пылесос REDMOND VH1319</t>
+          <t>Кофемашина REDMOND RCM-1517</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -14766,6 +15545,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M304" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -14776,12 +15558,12 @@
     <row r="305">
       <c r="B305" t="inlineStr">
         <is>
-          <t>Кофемашина REDMOND RCM-1517</t>
+          <t>Вертикальный беспроводной пылесос REDMOND VH1318 PRO MAX</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Кофемашина REDMOND RCM-1517</t>
+          <t>Вертикальный беспроводной пылесос REDMOND VH1318 PRO MAX</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -14813,6 +15595,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M305" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -14823,12 +15608,12 @@
     <row r="306">
       <c r="B306" t="inlineStr">
         <is>
-          <t>Вертикальный беспроводной пылесос REDMOND VH1318 PRO MAX</t>
+          <t>Умный электрический чайник REDMOND KG225</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Вертикальный беспроводной пылесос REDMOND VH1318 PRO MAX</t>
+          <t>Умный электрический чайник REDMOND KG225</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -14860,6 +15645,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M306" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -14870,12 +15658,12 @@
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
-          <t>Умный электрический чайник REDMOND KG225</t>
+          <t>Классический электрический чайник REDMOND KM235</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Умный электрический чайник REDMOND KG225</t>
+          <t>Классический электрический чайник REDMOND KM235</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -14907,6 +15695,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M307" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -14917,12 +15708,12 @@
     <row r="308">
       <c r="B308" t="inlineStr">
         <is>
-          <t>Классический электрический чайник REDMOND KM235</t>
+          <t>Электрический чайник с терморегулятором REDMOND KM245</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Классический электрический чайник REDMOND KM235</t>
+          <t>Электрический чайник с терморегулятором REDMOND KM245</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -14954,6 +15745,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M308" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -14964,12 +15758,12 @@
     <row r="309">
       <c r="B309" t="inlineStr">
         <is>
-          <t>Электрический чайник с терморегулятором REDMOND KM245</t>
+          <t>Электрический чайник с терморегулятором REDMOND KM250</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Электрический чайник с терморегулятором REDMOND KM245</t>
+          <t>Электрический чайник с терморегулятором REDMOND KM250</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -15001,6 +15795,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M309" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -15011,12 +15808,12 @@
     <row r="310">
       <c r="B310" t="inlineStr">
         <is>
-          <t>Электрический чайник с терморегулятором REDMOND KM250</t>
+          <t>Умный электрический чайник REDMOND SkyKettle KG258S</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Электрический чайник с терморегулятором REDMOND KM250</t>
+          <t>Умный электрический чайник REDMOND SkyKettle KG258S</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -15048,6 +15845,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -15058,12 +15858,12 @@
     <row r="311">
       <c r="B311" t="inlineStr">
         <is>
-          <t>Умный электрический чайник REDMOND SkyKettle KG258S</t>
+          <t>Увлажнитель воздуха Smartmi Evaporative Humidifier 2 (модель CJXJSQ04ZM)</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Умный электрический чайник REDMOND SkyKettle KG258S</t>
+          <t>Увлажнитель воздуха Smartmi Evaporative Humidifier 2 (модель CJXJSQ04ZM)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -15095,6 +15895,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>1.114</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -15105,12 +15908,12 @@
     <row r="312">
       <c r="B312" t="inlineStr">
         <is>
-          <t>Увлажнитель воздуха Smartmi Evaporative Humidifier 2 (модель CJXJSQ04ZM)</t>
+          <t>Беспроводной вертикальный пылесос Xiaomi Roidmi F8 / S1 (код модели XCQ03RM)</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Увлажнитель воздуха Smartmi Evaporative Humidifier 2 (модель CJXJSQ04ZM)</t>
+          <t>Беспроводной вертикальный пылесос Xiaomi Roidmi F8 / S1 (код модели XCQ03RM)</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -15142,6 +15945,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -15152,12 +15958,12 @@
     <row r="313">
       <c r="B313" t="inlineStr">
         <is>
-          <t>Беспроводной вертикальный пылесос Xiaomi Roidmi F8 / S1 (код модели XCQ03RM)</t>
+          <t>Рожковая кофеварка с автокапучинатором REDMOND CM714</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Беспроводной вертикальный пылесос Xiaomi Roidmi F8 / S1 (код модели XCQ03RM)</t>
+          <t>Рожковая кофеварка с автокапучинатором REDMOND CM714</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -15189,6 +15995,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -15199,12 +16008,12 @@
     <row r="314">
       <c r="B314" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка с автокапучинатором REDMOND CM714</t>
+          <t>Электрическая мясорубка-мультисистема REDMOND MG500</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Рожковая кофеварка с автокапучинатором REDMOND CM714</t>
+          <t>Электрическая мясорубка-мультисистема REDMOND MG500</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -15236,6 +16045,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M314" s="2" t="n">
+        <v>3.4</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -15246,12 +16058,12 @@
     <row r="315">
       <c r="B315" t="inlineStr">
         <is>
-          <t>Электрическая мясорубка-мультисистема REDMOND MG500</t>
+          <t>Мультипекарь REDMOND MB1201</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Электрическая мясорубка-мультисистема REDMOND MG500</t>
+          <t>Мультипекарь REDMOND MB1201</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -15284,6 +16096,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M315" s="2" t="n"/>
       <c r="O315" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15293,12 +16106,12 @@
     <row r="316">
       <c r="B316" t="inlineStr">
         <is>
-          <t>Мультипекарь REDMOND MB1201</t>
+          <t>Беспроводной моющий пылесос премиум-сегмента REDMOND MultiClean VH1316</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Мультипекарь REDMOND MB1201</t>
+          <t>Беспроводной моющий пылесос премиум-сегмента REDMOND MultiClean VH1316</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -15330,6 +16143,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M316" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -15340,12 +16156,12 @@
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
-          <t>Беспроводной моющий пылесос премиум-сегмента REDMOND MultiClean VH1316</t>
+          <t>Беспроводной вертикальный пылесос REDMOND VH1310</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Беспроводной моющий пылесос премиум-сегмента REDMOND MultiClean VH1316</t>
+          <t>Беспроводной вертикальный пылесос REDMOND VH1310</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -15377,6 +16193,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M317" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -15387,12 +16206,12 @@
     <row r="318">
       <c r="B318" t="inlineStr">
         <is>
-          <t>Беспроводной вертикальный пылесос REDMOND VH1310</t>
+          <t>Мультиварка REDMOND MC102 Color Chef</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Беспроводной вертикальный пылесос REDMOND VH1310</t>
+          <t>Мультиварка REDMOND MC102 Color Chef</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -15425,6 +16244,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M318" s="2" t="n"/>
       <c r="O318" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15434,12 +16254,12 @@
     <row r="319">
       <c r="B319" t="inlineStr">
         <is>
-          <t>Мультиварка REDMOND MC102 Color Chef</t>
+          <t>Компактная мультиварка REDMOND MC128</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Мультиварка REDMOND MC102 Color Chef</t>
+          <t>Компактная мультиварка REDMOND MC128</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -15472,6 +16292,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M319" s="2" t="n"/>
       <c r="O319" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15481,12 +16302,12 @@
     <row r="320">
       <c r="B320" t="inlineStr">
         <is>
-          <t>Компактная мультиварка REDMOND MC128</t>
+          <t>Электрическая сушилка-дегидратор горизонтального типа REDMOND FD1105</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Компактная мультиварка REDMOND MC128</t>
+          <t>Электрическая сушилка-дегидратор горизонтального типа REDMOND FD1105</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -15518,6 +16339,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M320" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -15528,12 +16352,12 @@
     <row r="321">
       <c r="B321" t="inlineStr">
         <is>
-          <t>Электрическая сушилка-дегидратор горизонтального типа REDMOND FD1105</t>
+          <t>Автоматическая зерновая кофемашина REDMOND RCM-1526</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Электрическая сушилка-дегидратор горизонтального типа REDMOND FD1105</t>
+          <t>Автоматическая зерновая кофемашина REDMOND RCM-1526</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -15565,6 +16389,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M321" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -15575,12 +16402,12 @@
     <row r="322">
       <c r="B322" t="inlineStr">
         <is>
-          <t>Автоматическая зерновая кофемашина REDMOND RCM-1526</t>
+          <t>Автоматическая кофемашина REDMOND CM710</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Автоматическая зерновая кофемашина REDMOND RCM-1526</t>
+          <t>Автоматическая кофемашина REDMOND CM710</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -15612,6 +16439,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M322" s="2" t="n">
+        <v>2.61</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -15622,12 +16452,12 @@
     <row r="323">
       <c r="B323" t="inlineStr">
         <is>
-          <t>Автоматическая кофемашина REDMOND CM710</t>
+          <t>Парогенератор Red Solution (Redmond) RSS-5906</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Автоматическая кофемашина REDMOND CM710</t>
+          <t>Парогенератор Red Solution (Redmond) RSS-5906</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -15659,6 +16489,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M323" s="2" t="n">
+        <v>2.583</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -15669,12 +16502,12 @@
     <row r="324">
       <c r="B324" t="inlineStr">
         <is>
-          <t>Парогенератор Red Solution (Redmond) RSS-5906</t>
+          <t>Cушилка для овощей и фруктов (дегидратор) RED SOLUTION DD011V</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Парогенератор Red Solution (Redmond) RSS-5906</t>
+          <t>Cушилка для овощей и фруктов (дегидратор) RED SOLUTION DD011V</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -15706,6 +16539,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M324" s="2" t="n">
+        <v>2.95</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -15716,12 +16552,12 @@
     <row r="325">
       <c r="B325" t="inlineStr">
         <is>
-          <t>Cушилка для овощей и фруктов (дегидратор) RED SOLUTION DD011V</t>
+          <t>Умный робот-мойщик окон RED SOLUTION SkyWiper RV-RW001S</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Cушилка для овощей и фруктов (дегидратор) RED SOLUTION DD011V</t>
+          <t>Умный робот-мойщик окон RED SOLUTION SkyWiper RV-RW001S</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -15754,6 +16590,7 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M325" s="2" t="n"/>
       <c r="O325" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15763,12 +16600,12 @@
     <row r="326">
       <c r="B326" t="inlineStr">
         <is>
-          <t>Умный робот-мойщик окон RED SOLUTION SkyWiper RV-RW001S</t>
+          <t>Многофункциональная шнековая соковыжималка «2 в 1» RED SOLUTION RJ-912S</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Умный робот-мойщик окон RED SOLUTION SkyWiper RV-RW001S</t>
+          <t>Многофункциональная шнековая соковыжималка «2 в 1» RED SOLUTION RJ-912S</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -15800,6 +16637,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M326" s="2" t="n">
+        <v>3.46</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -15810,12 +16650,12 @@
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
-          <t>Многофункциональная шнековая соковыжималка «2 в 1» RED SOLUTION RJ-912S</t>
+          <t>Термопот Midea MP-8105</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Многофункциональная шнековая соковыжималка «2 в 1» RED SOLUTION RJ-912S</t>
+          <t>Термопот Midea MP-8105</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -15847,6 +16687,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M327" s="2" t="n">
+        <v>2.1</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -15857,12 +16700,12 @@
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>Термопот Midea MP-8105</t>
+          <t>Электрический термопот Midea MP-8104</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Термопот Midea MP-8105</t>
+          <t>Электрический термопот Midea MP-8104</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -15894,6 +16737,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M328" s="2" t="n">
+        <v>2.1</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -15904,12 +16750,12 @@
     <row r="329">
       <c r="B329" t="inlineStr">
         <is>
-          <t>Электрический термопот Midea MP-8104</t>
+          <t>Аэрогриль Midea MAF-1040</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Электрический термопот Midea MP-8104</t>
+          <t>Аэрогриль Midea MAF-1040</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -15941,6 +16787,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M329" s="2" t="n">
+        <v>5.66</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -15951,12 +16800,12 @@
     <row r="330">
       <c r="B330" t="inlineStr">
         <is>
-          <t>Аэрогриль Midea MAF-1040</t>
+          <t>Кофейная станция REDMOND CM737</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Аэрогриль Midea MAF-1040</t>
+          <t>Кофейная станция REDMOND CM737</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -15988,6 +16837,9 @@
         <is>
           <t>FIFO</t>
         </is>
+      </c>
+      <c r="M330" s="2" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -15998,12 +16850,12 @@
     <row r="331">
       <c r="B331" t="inlineStr">
         <is>
-          <t>Кофейная станция REDMOND CM737</t>
+          <t>Аэрогриль Midea MAF-TN45WK</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Кофейная станция REDMOND CM737</t>
+          <t>Аэрогриль Midea MAF-TN45WK</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -16036,54 +16888,10 @@
           <t>FIFO</t>
         </is>
       </c>
+      <c r="M331" s="2" t="n">
+        <v>5.66</v>
+      </c>
       <c r="O331" t="inlineStr">
-        <is>
-          <t>Основная номенклатурная группа</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Аэрогриль Midea MAF-TN45WK</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Аэрогриль Midea MAF-TN45WK</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>Товары</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="J332" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>Без НДС</t>
-        </is>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>FIFO</t>
-        </is>
-      </c>
-      <c r="O332" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
         </is>

--- a/public/converted/nomenklatura-ot-bah-30-10-26.xlsx
+++ b/public/converted/nomenklatura-ot-bah-30-10-26.xlsx
@@ -2776,7 +2776,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2824,7 +2826,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
+      <c r="M47" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -2872,7 +2876,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n"/>
+      <c r="M48" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3220,7 +3226,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n"/>
+      <c r="M55" s="2" t="n">
+        <v>0.61</v>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3268,7 +3276,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
+      <c r="M56" s="2" t="n">
+        <v>0.61</v>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3516,7 +3526,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n"/>
+      <c r="M61" s="2" t="n">
+        <v>1.05</v>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -3564,7 +3576,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M62" s="2" t="n"/>
+      <c r="M62" s="2" t="n">
+        <v>1.05</v>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -4662,7 +4676,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M84" s="2" t="n"/>
+      <c r="M84" s="2" t="n">
+        <v>0.35</v>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5710,7 +5726,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M105" s="2" t="n"/>
+      <c r="M105" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5758,7 +5776,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M106" s="2" t="n"/>
+      <c r="M106" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O106" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5806,7 +5826,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n"/>
+      <c r="M107" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O107" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5854,7 +5876,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n"/>
+      <c r="M108" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O108" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5902,7 +5926,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M109" s="2" t="n"/>
+      <c r="M109" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O109" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5950,7 +5976,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M110" s="2" t="n"/>
+      <c r="M110" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O110" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -5998,7 +6026,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M111" s="2" t="n"/>
+      <c r="M111" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O111" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6046,7 +6076,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M112" s="2" t="n"/>
+      <c r="M112" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O112" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6094,7 +6126,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M113" s="2" t="n"/>
+      <c r="M113" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6142,7 +6176,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
+      <c r="M114" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O114" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6190,7 +6226,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M115" s="2" t="n"/>
+      <c r="M115" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O115" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6238,7 +6276,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M116" s="2" t="n"/>
+      <c r="M116" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O116" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6286,7 +6326,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M117" s="2" t="n"/>
+      <c r="M117" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O117" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6334,7 +6376,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M118" s="2" t="n"/>
+      <c r="M118" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O118" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6382,7 +6426,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M119" s="2" t="n"/>
+      <c r="M119" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O119" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6430,7 +6476,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M120" s="2" t="n"/>
+      <c r="M120" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O120" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6478,7 +6526,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M121" s="2" t="n"/>
+      <c r="M121" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O121" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6526,7 +6576,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M122" s="2" t="n"/>
+      <c r="M122" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6574,7 +6626,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M123" s="2" t="n"/>
+      <c r="M123" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6622,7 +6676,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M124" s="2" t="n"/>
+      <c r="M124" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O124" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6670,7 +6726,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M125" s="2" t="n"/>
+      <c r="M125" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6718,7 +6776,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M126" s="2" t="n"/>
+      <c r="M126" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6766,7 +6826,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M127" s="2" t="n"/>
+      <c r="M127" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6914,7 +6976,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M130" s="2" t="n"/>
+      <c r="M130" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="O130" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -6962,7 +7026,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M131" s="2" t="n"/>
+      <c r="M131" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="O131" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7010,7 +7076,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M132" s="2" t="n"/>
+      <c r="M132" s="2" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7058,7 +7126,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M133" s="2" t="n"/>
+      <c r="M133" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O133" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7106,7 +7176,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M134" s="2" t="n"/>
+      <c r="M134" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O134" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7154,7 +7226,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M135" s="2" t="n"/>
+      <c r="M135" s="2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="O135" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -7952,7 +8026,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M151" s="2" t="n"/>
+      <c r="M151" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O151" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -8000,7 +8076,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M152" s="2" t="n"/>
+      <c r="M152" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O152" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -8048,7 +8126,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M153" s="2" t="n"/>
+      <c r="M153" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O153" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -9796,7 +9876,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M188" s="2" t="n"/>
+      <c r="M188" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O188" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -9844,7 +9926,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M189" s="2" t="n"/>
+      <c r="M189" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O189" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10842,7 +10926,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M209" s="2" t="n"/>
+      <c r="M209" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O209" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10890,7 +10976,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M210" s="2" t="n"/>
+      <c r="M210" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O210" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -10938,7 +11026,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M211" s="2" t="n"/>
+      <c r="M211" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O211" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -11286,7 +11376,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M218" s="2" t="n"/>
+      <c r="M218" s="2" t="n">
+        <v>2.3</v>
+      </c>
       <c r="O218" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -11384,7 +11476,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M220" s="2" t="n"/>
+      <c r="M220" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O220" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -11532,7 +11626,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M223" s="2" t="n"/>
+      <c r="M223" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12530,7 +12626,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M243" s="2" t="n"/>
+      <c r="M243" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O243" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -12978,7 +13076,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M252" s="2" t="n"/>
+      <c r="M252" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O252" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13276,7 +13376,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M258" s="2" t="n"/>
+      <c r="M258" s="2" t="n">
+        <v>2.65</v>
+      </c>
       <c r="O258" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13324,7 +13426,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M259" s="2" t="n"/>
+      <c r="M259" s="2" t="n">
+        <v>2.65</v>
+      </c>
       <c r="O259" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13372,7 +13476,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M260" s="2" t="n"/>
+      <c r="M260" s="2" t="n">
+        <v>2.65</v>
+      </c>
       <c r="O260" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13620,7 +13726,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M265" s="2" t="n"/>
+      <c r="M265" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O265" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -13668,7 +13776,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M266" s="2" t="n"/>
+      <c r="M266" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="O266" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14166,7 +14276,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M276" s="2" t="n"/>
+      <c r="M276" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="O276" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14614,7 +14726,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M285" s="2" t="n"/>
+      <c r="M285" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O285" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14712,7 +14826,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M287" s="2" t="n"/>
+      <c r="M287" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O287" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14760,7 +14876,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M288" s="2" t="n"/>
+      <c r="M288" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O288" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14908,7 +15026,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M291" s="2" t="n"/>
+      <c r="M291" s="2" t="n">
+        <v>7.5</v>
+      </c>
       <c r="O291" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -14956,7 +15076,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M292" s="2" t="n"/>
+      <c r="M292" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O292" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15004,7 +15126,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M293" s="2" t="n"/>
+      <c r="M293" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O293" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15302,7 +15426,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M299" s="2" t="n"/>
+      <c r="M299" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O299" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15400,7 +15526,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M301" s="2" t="n"/>
+      <c r="M301" s="2" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O301" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -15448,7 +15576,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M302" s="2" t="n"/>
+      <c r="M302" s="2" t="n">
+        <v>2.1</v>
+      </c>
       <c r="O302" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -16096,7 +16226,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M315" s="2" t="n"/>
+      <c r="M315" s="2" t="n">
+        <v>1.66</v>
+      </c>
       <c r="O315" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -16244,7 +16376,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M318" s="2" t="n"/>
+      <c r="M318" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O318" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -16292,7 +16426,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M319" s="2" t="n"/>
+      <c r="M319" s="2" t="n">
+        <v>2.265</v>
+      </c>
       <c r="O319" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
@@ -16590,7 +16726,9 @@
           <t>FIFO</t>
         </is>
       </c>
-      <c r="M325" s="2" t="n"/>
+      <c r="M325" s="2" t="n">
+        <v>1.05</v>
+      </c>
       <c r="O325" t="inlineStr">
         <is>
           <t>Основная номенклатурная группа</t>
